--- a/artfynd/A 3033-2023 artfynd.xlsx
+++ b/artfynd/A 3033-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958844</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959059</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968574</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969208</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970185</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956247</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134961258</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134962830</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968162</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968573</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970403</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955413</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955415</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134955843</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958429</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2228,6 +2308,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967946</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971030</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964279</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965414</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2620,6 +2720,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970404</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2717,6 +2822,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969209</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2814,6 +2924,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971244</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2911,6 +3026,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956876</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3008,6 +3128,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958207</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3105,6 +3230,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959057</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3202,6 +3332,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968575</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3299,8 +3434,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970184</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 3033-2023 artfynd.xlsx
+++ b/artfynd/A 3033-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134958844</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>134959059</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>134968574</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>134969208</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>134970185</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>134956247</v>
       </c>
       <c r="B7" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>134961258</v>
       </c>
       <c r="B8" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>134962830</v>
       </c>
       <c r="B9" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>134968162</v>
       </c>
       <c r="B10" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>134968573</v>
       </c>
       <c r="B11" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>134970403</v>
       </c>
       <c r="B12" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>134955413</v>
       </c>
       <c r="B13" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>134955415</v>
       </c>
       <c r="B14" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>134955843</v>
       </c>
       <c r="B15" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>134958429</v>
       </c>
       <c r="B16" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>134967946</v>
       </c>
       <c r="B17" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>134971030</v>
       </c>
       <c r="B18" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>134964279</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>134965414</v>
       </c>
       <c r="B20" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>134970404</v>
       </c>
       <c r="B21" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>134969209</v>
       </c>
       <c r="B22" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>134971244</v>
       </c>
       <c r="B23" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>134956876</v>
       </c>
       <c r="B24" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>134958207</v>
       </c>
       <c r="B25" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>134959057</v>
       </c>
       <c r="B26" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>134968575</v>
       </c>
       <c r="B27" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>134970184</v>
       </c>
       <c r="B28" t="n">
-        <v>100220</v>
+        <v>100267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
